--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0105.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0105.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Phần thưởng đã nhận</t>
+          <t>Đã nhận phần thưởng</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Hoàn thành lần đầu</t>
+          <t>Hoàn Thành Lần Đầu</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Điều Chỉnh Đội Hình</t>
+          <t>Điều chỉnh đội hình</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Nhấn phím bạn muốn thiết lập</t>
+          <t>Nhấn phím bạn muốn thiết lập.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Thay đổi câu cuối</t>
+          <t>Thay đổi câu cuối cùng</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Replace</t>
+          <t>Thay thế</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Khoảng cách gửi tin nhắn quá ngắn</t>
+          <t>Khoảng thời gian gửi tin nhắn quá ngắn</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Không Record</t>
+          <t>Không có bản ghi</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Hoàn thành khám phá trước để mở khóa</t>
+          <t>Hoàn thành chuyến thám hiểm trước để mở khóa</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bạn cần hoàn thành khám phá khu vực trước để thách đấu</t>
+          <t>Ngươi cần hoàn thành việc khám phá khu vực trước đó để có thể thách đấu.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Chạm để hạ cánh tại Solaris-3</t>
+          <t>Chạm để hạ cánh xuống Solaris-3</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Đăng nhập vào trò chơi</t>
+          <t>Đăng nhập vào game</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Synthesize</t>
+          <t>Tổng hợp</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Cấp độ Tổng hợp</t>
+          <t>Cấp Độ Tổng Hợp</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Cấp độ Dược sư</t>
+          <t>Cấp độ Dược Sư</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Chọn một Resonator hỗ trợ bạn:</t>
+          <t>Chọn Resonator hỗ trợ bạn:</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Hoàn tất</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Lên Cấp</t>
+          <t>Nâng cấp Nhiệm vụ</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Synthesize</t>
+          <t>Tổng hợp</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Số lượng</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Cấp độ Đầu bếp</t>
+          <t>Cấp Độ Đầu Bếp</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Cấp độ Đầu bếp</t>
+          <t>Cấp Độ Đầu Bếp</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Vật liệu Nghiên cứu Ẩm thực không đủ</t>
+          <t>Không đủ nguyên liệu cho Nghiên Cứu Ẩm Thực</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Chọn nguyên liệu cho Nghiên cứu Ẩm thực</t>
+          <t>Chọn nguyên liệu cho Nghiên Cứu Ẩm Thực</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Promotion</t>
+          <t>Thăng Cấp</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Việc khám phá tầng này đã hoàn tất</t>
+          <t>Việc thám hiểm tầng này đã hoàn tất.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Bậc Thầy Âm Phách</t>
+          <t>Chủ Âm Thanh Ảo</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Heterogeneous Residual Sound</t>
+          <t>Âm Thanh Dư Vọng Bất Đồng</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Đang tổng hợp dữ liệu</t>
+          <t>Đang tổng hợp dữ liệu...</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Đội hình của những người chơi khác vừa đạt điểm tuyệt đối trong lần đầu vượt ải</t>
+          <t>Đội hình của các Cộng Hưởng Giả khác vừa đạt điểm tuyệt đối ngay lần đầu vượt ải</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Resonator này không thể cung cấp bonus khi tổng hợp vật phẩm này</t>
+          <t>Resonator này không thể tăng hiệu quả khi tổng hợp vật phẩm này</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Resonator này không thể cung cấp bonus khi chế tạo vũ khí này</t>
+          <t>Resonator này không thể tăng hiệu quả khi chế tạo vũ khí này</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Resonator này không thể cung cấp bonus khi nấu món ăn này</t>
+          <t>Resonator này không thể tăng hiệu quả khi nấu món này</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Unfriended</t>
+          <t>Hủy Kết Bạn</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Uninstall</t>
+          <t>Gỡ bỏ</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Xóa thư đã đọc</t>
+          <t>Xóa Thư Đã Đọc</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Detect</t>
+          <t>Dò tìm</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Sẽ nhận được phần thưởng gấp đôi cho lần mua đầu tiên của mỗi trang bị</t>
+          <t>Mua trang bị lần đầu sẽ được hoàn trả phần thưởng nhân đôi</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Downloaded</t>
+          <t>Đã tải xong</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Tải Xuống</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Echo Dropped</t>
+          <t>Tiếng Vọng Rơi Rớt</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Có nhân vật trong đội hiện tại không đủ Vigor</t>
+          <t>Có một Cộng Hưởng Giả trong đội hình hiện tại không đủ Sinh Lực.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình khi đang leo trèo</t>
+          <t>Không thể thay đổi đội hình khi đang leo trèo</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình khi đang nhảy</t>
+          <t>Không thể thay đổi đội hình khi đang nhảy</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình trong chiến đấu</t>
+          <t>Không thể thay đổi đội hình trong trận chiến</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình ở trạng thái hiện tại</t>
+          <t>Không thể thay đổi đội hình ở trạng thái hiện tại</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình khi đang bơi</t>
+          <t>Không thể thay đổi đội hình khi đang bơi</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Nhân vật đã được triển khai</t>
+          <t>Đã triển khai {CharacterName}</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Cần ít nhất một nhân vật trong đội</t>
+          <t>Cần ít nhất một Cộng Hưởng Giả trong đội</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Không có nhân vật khả dụng trong đội hiện tại, không thể triển khai</t>
+          <t>Không có Cộng Hưởng Giả nào khả dụng trong đội hiện tại, không thể triển khai.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Không có nhân vật khả dụng trong đội hiện tại, không thể thay đổi</t>
+          <t>Không có Cộng Hưởng Giả nào khả dụng trong đội hiện tại, không thể thay đổi.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Edit Đội</t>
+          <t>Chỉnh sửa đội hình</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Cần ít nhất một Resonator chưa bị hạ gục</t>
+          <t>Ít nhất cũng phải có một Resonator không bị hạ gục.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Chưa thêm nhân vật</t>
+          <t>Chưa thêm {CharacterName}</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Fusion</t>
+          <t>Hợp Nhất</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Kết Thúc</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Redeemed</t>
+          <t>Đã đổi</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Thi hành án</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Thám hiểm thất bại</t>
+          <t>Thám Hiểm Thất Bại</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Hoàn thành thám hiểm</t>
+          <t>Hoàn Thành Thám Hiểm</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Exploration Finish</t>
+          <t>Hoàn Thành Thám Hiểm</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Hiện không có nội dung</t>
+          <t>Hiện chưa có nội dung.</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Chưa có Tiện ích khả dụng</t>
+          <t>Chưa có Tiện Ích nào khả dụng</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Nhấn để chọn mục bánh xe</t>
+          <t>Nhấn để chọn mục trong vòng quay</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Chọn mục bánh xe này</t>
+          <t>Chọn mục này trên vòng quay</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Công cụ Wheel</t>
+          <t>Bánh xe tiện ích</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Chưa chọn ô</t>
+          <t>Chưa chọn lưới</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Vui lòng chọn một ô từ bánh xe bên trái để lắp ráp</t>
+          <t>Hãy chọn một ô lưới từ bánh xe bên trái để lắp ráp.</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Exploration</t>
+          <t>Thám Hiểm</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Character Animations</t>
+          <t>Hoạt ảnh Nhân vật</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Basic Information</t>
+          <t>Thông Tin Cơ Bản</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Intimacy</t>
+          <t>Thân Tình</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Backstory</t>
+          <t>Lý lịch</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Combat Animation</t>
+          <t>Hiệu Ứng Chiến Đấu</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Battle Voicelines</t>
+          <t>Lời Thoại Trong Trận Đấu</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Archive-Echo</t>
+          <t>Echo Lưu Trữ</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Idle Animation</t>
+          <t>Động tác chờ</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Personal Voicelines</t>
+          <t>Lời thoại cá nhân</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Vật phẩm Yêu thích</t>
+          <t>Vật Phẩm Quý Giá</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Archives</t>
+          <t>Kho lưu trữ</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Character Stories</t>
+          <t>Câu chuyện Nhân vật</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Mở khóa Động tác Chiến đấu mới</t>
+          <t>Mở khóa Động Tác Chiến Đấu mới</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Entry Locked</t>
+          <t>Đã Khóa Vào cửa</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Mở khóa trạng thái chờ mới</t>
+          <t>Mở khóa trạng thái đứng yên mới</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Entry Locked</t>
+          <t>Đã Khóa Vào cửa</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Entry Locked</t>
+          <t>Đã Khóa Vào cửa</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Entry Locked</t>
+          <t>Đã Khóa Vào cửa</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Character Voicelines</t>
+          <t>Lời thoại nhân vật</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Match Dungeon</t>
+          <t>Phó bản thi đấu</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Sonata Effect</t>
+          <t>Hiệu Ứng Sonata</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Combat Skills</t>
+          <t>Kỹ Năng Chiến Đấu</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Bộ lọc</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Đặt lại Done</t>
+          <t>Đã đặt lại</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Sắp xếp</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Lọc và Sắp xếp</t>
+          <t>Lọc và Sắp Xếp</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Filter On/Off</t>
+          <t>Bật/Tắt Bộ Lọc</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Bộ lọc</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Phần Thưởng</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Phần thưởng Hoàn thành lần đầu</t>
+          <t>Phần Thưởng Lần Đầu Vượt Ải</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Vui lòng tiếp tục nhiệm vụ theo mục tiêu</t>
+          <t>Hãy tiếp tục nhiệm vụ theo chỉ dẫn mục tiêu</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Không thể thực hiện hành động này khi đang ở giữa không trung</t>
+          <t>Không thể thực hiện hành động này khi đang ở trên không.</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vĩnh viễn</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Crafting Completed</t>
+          <t>Hoàn thành chế tác</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Crafting</t>
+          <t>Đang chế tác</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Công thức</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Thêm bạn bè</t>
+          <t>Thêm Bạn Bè</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Chấp nhận tất cả</t>
+          <t>Chấp Nhận Tất Cả</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Ignore Tất cả</t>
+          <t>Bỏ Qua Toàn Bộ</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Friend Request</t>
+          <t>Yêu Cầu Kết Bạn</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Tham gia Hợp tác</t>
+          <t>Tham Gia Hợp Tác</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Blocklist</t>
+          <t>Danh sách chặn</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Không Friend Request</t>
+          <t>Không có lời mời kết bạn</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Không Gần đây Co-ops</t>
+          <t>Chưa tham gia hợp tác gần đây</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Chế độ Co-op không khả dụng</t>
+          <t>Không Thể Hợp Tác</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Đang trực tuyến</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Paste</t>
+          <t>Hồ dán</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Gần đây Co-ops</t>
+          <t>Hợp tác gần đây</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Nhấn luân phiên để thoát</t>
+          <t>Nhấn luân phiên để thoát ra</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Hiện không có mục chức năng nhanh để lắp ráp</t>
+          <t>Hiện tại không có mục chức năng nhanh nào để lắp ráp cả</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Quick Access</t>
+          <t>Truy cập nhanh</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Thả ra để kích hoạt</t>
+          <t>Thả để kích hoạt</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Quick Access Wheel</t>
+          <t>Bánh xe truy cập nhanh</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Chọn Resonator để Triệu Hoán Mục Tiêu</t>
+          <t>Chọn Resonator để Triệu Hồi Có Mục Tiêu</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Chọn Vũ Khí để Triệu Hoán Mục Tiêu</t>
+          <t>Chọn Vũ Khí để Triệu Hồi Mục Tiêu</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Đã chọn</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Targeted Triệu Tập</t>
+          <t>Triệu Hồi Có Mục Tiêu</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Lịch sử Triệu Hoán</t>
+          <t>Lịch sử triệu tập</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>20% OFF</t>
+          <t>GIẢM 20%</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>EVENT</t>
+          <t>SỰ KIỆN</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>LỰA CHỌN</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>KHỞI ĐỘNG</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Mới</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Triệu Hồi Tân Thủ</t>
+          <t>Tập Hợp Tân Thủ</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Featured Resonator Triệu Tập</t>
+          <t>Triệu Hồi Resonator Đặc Sắc</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Featured Weapon Triệu Tập</t>
+          <t>Triệu Hồi Vũ Khí Đặc Sắc</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Resonator Triệu Tập</t>
+          <t>Triệu hồi Resonator tiêu chuẩn</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Weapon Triệu Tập</t>
+          <t>Triệu Hồi Vũ Khí Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Beginner's Choice Triệu Tập</t>
+          <t>Gói Triệu Hồi Lựa Chọn Dành Cho Tân Thủ</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Anniversary Resonator Triệu Tập</t>
+          <t>Triệu hồi Resonator kỷ niệm</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Anniversary Weapon Triệu Tập</t>
+          <t>Triệu hồi Vũ khí kỷ niệm</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>New Voyage Resonator Triệu Tập</t>
+          <t>Hành Trình Mới - Triệu Hồi Resonator</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>New Voyage Weapon Triệu Tập</t>
+          <t>Hành Trình Mới - Triệu Hồi Vũ Khí</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Loại Triệu Hoán</t>
+          <t>Loại triệu tập</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>4-Star Resonators Rate Up</t>
+          <t>Tăng Tỷ Lệ Resonator 4 Sao</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>4-Star Weapons Rate Up</t>
+          <t>Tăng Tỷ Lệ Vũ Khí 4 Sao</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Cảnh Báo</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Domain Cleared</t>
+          <t>Đã Diệt Tổ Tacet</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Converted</t>
+          <t>Đã chuyển đổi</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Vật phẩm Obtained</t>
+          <t>Đã nhận được vật phẩm</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Rover (Nữ)</t>
+          <t>Vận Mệnh Giả (Nữ)</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Unselect</t>
+          <t>Bỏ chọn</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tiến đến khu vực đã chọn</t>
+          <t>Tiến vào Khu Vực Đã Chọn</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Tải xuống</t>
+          <t>Tải xuống thôi</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Thư viện</t>
+          <t>Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Bộ Điều Khiển</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Phần thưởng Thám Hiểm đã được nhận trước</t>
+          <t>Phần Thưởng Thám Hiểm Đã Nhận Trước</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Request Sent</t>
+          <t>Nhiệm Vụ Đã Gửi</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Lời mời đã được gửi</t>
+          <t>Đã gửi lời mời</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Mời đồng đội tham gia</t>
+          <t>Đang mời đồng đội tham gia</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Anh ấy</t>
+          <t>Hắn</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Grapple</t>
+          <t>Móc Câu</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>giờ</t>
+          <t>hừ</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Lỗi không xác định</t>
+          <t>Lỗi Không Xác Định</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Immune</t>
+          <t>Miễn nhiễm</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Starred Mails</t>
+          <t>Thư Từ Vì Sao</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Giọng lồng tiếng đang sử dụng không thể gỡ cài đặt</t>
+          <t>Giọng lồng tiếng đang sử dụng không thể gỡ bỏ.</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Chứa vật phẩm</t>
+          <t>Có chứa vật phẩm</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Phe phái liên kết không cần tích lũy Ảnh hưởng</t>
+          <t>Phe phái liên kết không cần tích lũy Ảnh Hưởng</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Phe phái thù địch không thể tích lũy Ảnh hưởng</t>
+          <t>Phe đối địch không thể tích lũy Ảnh Hưởng</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Vui lòng không đóng game trong quá trình cài đặt</t>
+          <t>Xin đừng tắt game trong quá trình cài đặt.</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Hiện tại bạn không thể quay về chế độ chơi đơn</t>
+          <t>Hiện tại bạn không thể quay về chế độ chơi đơn.</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Points Acquired</t>
+          <t>Đã nhận Điểm</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Hủy Theo dõi</t>
+          <t>Hủy theo dõi</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện truy cập vào lối vào</t>
+          <t>Chưa đáp ứng điều kiện vào cửa</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Entrance Unlocked</t>
+          <t>Đã Mở Khóa Vào cửa</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Theo dõi</t>
+          <t>Bản nhạc</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Không đủ số lần thử thách</t>
+          <t>Không đủ lượt thử thách</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn nhận thưởng</t>
+          <t>Đã đạt giới hạn nhận thưởng.</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Hiện tại bạn không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Hiện tại bạn không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Không thể triệu hồi Phaom tại đây</t>
+          <t>Không thể triệu hồi Phaom ở đây</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Replace</t>
+          <t>Thay thế</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Mời bạn thử thách lại</t>
+          <t>Mời cậu thử thách lại</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Mời bạn tiếp tục thử thách</t>
+          <t>Mời cậu tiếp tục thử thách</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Mời bạn bè</t>
+          <t>Mời Bạn Bè</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Mời người chơi gần đó</t>
+          <t>Mời người chơi gần đây</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Nhân vật đã chọn đã có trong đội chiến đấu</t>
+          <t>Cộng Hưởng Giả đã chọn đã có mặt trong đội chiến đấu.</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Friend Added</t>
+          <t>Đã Thêm Bạn Bè</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể chuyển đổi nhân vật của mình</t>
+          <t>Bạn chỉ có thể đổi nhân vật thôi.</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Số lượng vật phẩm này không đáp ứng yêu cầu</t>
+          <t>Số lượng vật phẩm này không đáp ứng yêu cầu.</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Chưa nhận được vật phẩm</t>
+          <t>Bạn chưa nhận được vật phẩm này</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Bàn phím và chuột</t>
+          <t>Bàn Phím và Chuột</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Hủy ghép đội</t>
+          <t>Đã hủy ghép trận</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Đội trưởng đã rời đi, đội ghép đã giải tán</t>
+          <t>Đội trưởng đã rời đi, đội đấu đã bị giải tán</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Bên trái</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Đã rời khu vực</t>
+          <t>Khu vực bên trái</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Không có gói cấp độ khả dụng</t>
+          <t>Không có gói cấp độ nào khả dụng</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Đạt cấp tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Upgraded</t>
+          <t>Đã nâng cấp</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Số lượng Resonator trong trận không đáp ứng yêu cầu</t>
+          <t>Số lượng Cộng Hưởng Giả trong trận không đủ yêu cầu</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thử Lại</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Liên hệ hỗ trợ khách hàng</t>
+          <t>Liên hệ bộ phận chăm sóc khách hàng</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Log Uploaded</t>
+          <t>Đã tải nhật ký lên</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Upload</t>
+          <t>Tải lên</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Culinary Nghiên cứu</t>
+          <t>Nghiên Cứu Ẩm Thực</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Cắt và gia công</t>
+          <t>Cắt và xử lý</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kho lưu trữ</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Deleted</t>
+          <t>Đã xóa</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Vật phẩm Obtained</t>
+          <t>Đã nhận được vật phẩm</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>From:</t>
+          <t>Từ:</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Heading</t>
+          <t>Đang trên đường...</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Thư</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Đã nhận email mới</t>
+          <t>Đã nhận một email mới</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Ingredient Making</t>
+          <t>Chế biến Nguyên liệu</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Dish Making</t>
+          <t>Chế biến món ăn</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Craft</t>
+          <t>Chế Tạo</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Việc ghép trận sẽ tiếp tục</t>
+          <t>Ghép trận sẽ tiếp tục</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Prepare</t>
+          <t>Chuẩn bị</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Exit Matching</t>
+          <t>Hủy Ghép Đội</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Matching Ready</t>
+          <t>Sẵn sàng ghép trận</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Một số người chơi chưa xác nhận, đang ghép trận lại</t>
+          <t>Vẫn còn vài người chơi chưa xác nhận, đang ghép trận lại</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Match Complete</t>
+          <t>Trận đấu kết thúc</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Sắp được chuyển đến lối vào phiên bản</t>
+          <t>Sắp được chuyển đến lối vào phiên bản nhiệm vụ</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Vật phẩm</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Đã giao tối đa số vật phẩm</t>
+          <t>Đã giao số lượng vật phẩm tối đa</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Potion</t>
+          <t>Thuốc Tiềm Năng</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Giao Tất Cả</t>
+          <t>Giao tất cả</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Quay về Mức hiện tại</t>
+          <t>Trở lại Cấp Độ Hiện Tại</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Quay về Mức hiện tại</t>
+          <t>Trở lại Cấp Độ Hiện Tại</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ.</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ừm</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ừm</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Nhấn vào nửa phải màn hình để tự động nhặt</t>
+          <t>Nhấn vào nửa phải màn hình để tự động nhặt đồ</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Đặt lại sau</t>
+          <t>Đặt lại sau khi</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Animations</t>
+          <t>Hoạt Ảnh</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Trở về trò chơi đơn</t>
+          <t>Quay lại chế độ chơi đơn</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Mute</t>
+          <t>Im lặng</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Chỉ có thể thử lại thử thách sau khi tất cả thành viên trong đội bị hạ gục</t>
+          <t>Thử thách chỉ có thể thử lại sau khi tất cả thành viên trong đội bị đánh gục</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả các giai đoạn của độ khó trước để mở khóa</t>
+          <t>Hoàn thành tất cả các giai đoạn ở độ khó trước để mở khóa</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Connecting</t>
+          <t>Đang kết nối</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Hiện không có thông báo</t>
+          <t>Hiện chưa có thông báo nào</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hiện không hỗ trợ thay thế Nhân vật</t>
+          <t>Hiện không hỗ trợ thay đổi Nhân Vật</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Không Starred Mails</t>
+          <t>Không có Thư Đã Đánh Dấu</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Không Mails</t>
+          <t>Không có thư</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Không Unread Mails</t>
+          <t>Không có thư chưa đọc</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi nhân vật trong Chế độ Dùng Thử</t>
+          <t>Không thể đổi nhân vật trong Chế Độ Thử Nghiệm</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Nội dung nhập vào chứa ký tự nhạy cảm</t>
+          <t>Nội dung nhập vào chứa ký tự nhạy cảm.</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Số lượng vật phẩm không đủ</t>
+          <t>Số lượng vật phẩm không đủ.</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Vui lòng hoàn thành tất cả nhiệm vụ trong chương này</t>
+          <t>Hãy hoàn thành tất cả nhiệm vụ trong chương này</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành</t>
+          <t>Chưa Hoàn Tất</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Không có vật phẩm khả dụng để hồi sinh</t>
+          <t>Không có vật phẩm hồi sinh nào khả dụng</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Unavailable Area</t>
+          <t>Khu Vực Không Khả Dụng</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Ngoại tuyến</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Tôi...</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Đang ở Chế độ Hợp tác, không thể điều chỉnh Giai đoạn SOL3</t>
+          <t>Đang ở Chế Độ Hợp Tác, không thể điều chỉnh Giai Đoạn SOL3</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Bạn không thể mở Phòng Hợp tác khi đang trong thử thách</t>
+          <t>Bạn không thể mở Phòng Hợp Tác khi đang trong thử thách.</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>yêu cầu tham gia thế giới của bạn</t>
+          <t>yêu cầu tham gia thế giới của cậu</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Lựa chọn</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Produce Echo</t>
+          <t>Tạo Âm Hưởng</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Có thể thu nhỏ trò chơi trong quá trình tải xuống</t>
+          <t>Trò chơi có thể được thu nhỏ trong quá trình tải xuống.</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Tạm dừng tải xuống</t>
+          <t>Tải bản tạm dừng</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Pausing</t>
+          <t>Đang tạm dừng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Join Upon Approval</t>
+          <t>Tham Gia Khi Được Phê Duyệt</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Công cộng</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Đã đóng</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Bạn bè Only</t>
+          <t>Chỉ Bạn Bè</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Không có Echo giống nhau</t>
+          <t>Không trùng Echo</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Integrated Tunning</t>
+          <t>Điều chỉnh Tích hợp</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Tuning</t>
+          <t>Điều Chỉnh</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Sonata Details</t>
+          <t>Chi Tiết Sonata</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Not Equipped</t>
+          <t>Chưa Trang Bị</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Not Owned</t>
+          <t>Chưa sở hữu</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình trong trạng thái hiện tại</t>
+          <t>Không thể thay đổi đội hình ở trạng thái hiện tại</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Bạn không thể tham gia thử thách ở trạng thái hiện tại</t>
+          <t>Hiện tại bạn không thể tham gia thử thách ở trạng thái này.</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Không thể sử dụng Túi đồ ở trạng thái hiện tại</t>
+          <t>Không thể sử dụng Túi Đồ ở trạng thái hiện tại</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Bạn hiện không thể dịch chuyển</t>
+          <t>Hiện tại bạn không thể dịch chuyển.</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Không thể tham gia Hợp tác ở trạng thái hiện tại</t>
+          <t>Hiện không thể tham gia Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Không thể mở màn hình Resonator ở trạng thái hiện tại</t>
+          <t>Hiện không thể mở màn hình Resonator</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Đạt cấp tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Không có Echo cùng thuộc tính</t>
+          <t>Không có Echo cùng thuộc tính.</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Random Nâng cấp</t>
+          <t>Nâng Cấp Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Phantom Appearance On</t>
+          <t>Hiện Hình Ảo Ảnh Đang Bật</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Phantom Appearance Unlocked</t>
+          <t>Hiện Hình Ảo Ảnh Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>New Rarity Unlocked</t>
+          <t>Độ Hiếm Mới đã mở khóa</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Vui lòng chọn một vật phẩm trước</t>
+          <t>Hãy chọn vật phẩm trước</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Waveplate đã đầy</t>
+          <t>Bảng Tần Số đã đầy</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Bổ sung và Nhận</t>
+          <t>Bổ Sung Và Nhận</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Số lần mua hôm nay không đủ</t>
+          <t>Hôm nay đã hết lượt mua.</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Replenish Waveplate</t>
+          <t>Bổ Sung Waveplate</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Phần thưởng có thể nhận</t>
+          <t>Những Phần Thưởng Khả Thi</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Thả ra để chuyển đổi</t>
+          <t>Thả phím để chuyển đổi</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Công cụ Toggle Wheel</t>
+          <t>Bánh xe chuyển đổi tiện ích</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>Trống rỗng</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Thả ra để hủy</t>
+          <t>Thả để hủy</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Thả ra để chuyển đổi</t>
+          <t>Thả để bật/tắt</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Nhấn vào mục trong bánh xe để tùy chỉnh</t>
+          <t>Chọn một mục trong vòng tròn để tùy chỉnh</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Vui lòng chọn mục bên trái trước</t>
+          <t>Hãy chọn mục nhập bên trái trước</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Vui lòng chọn Công cụ để trang bị</t>
+          <t>Hãy chọn một Tiện ích để trang bị.</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Đặt lại mặc định</t>
+          <t>Đặt lại về mặc định</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Proficiency</t>
+          <t>Thành thạo</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Purification</t>
+          <t>Thanh Tẩy</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Vui lòng đặt đủ các vật phẩm cần thiết</t>
+          <t>Hãy đặt tất cả các vật phẩm cần thiết vào.</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Hòa Điệu</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Nhân vật nhiệm vụ không khả dụng</t>
+          <t>Nhân vật nhiệm vụ hiện không khả dụng</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>New Goal</t>
+          <t>Mục Tiêu Mới</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Thoát Thám hiểm</t>
+          <t>Thoát Khám Phá</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Thử lại thử thách</t>
+          <t>Thử lại Thử thách</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Đã đạt cấp tối đa</t>
+          <t>Đã đạt cấp bậc tối đa</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn hồi sinh hạ gục</t>
+          <t>Đã đạt giới hạn hồi sinh sau knockout</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Potion Making</t>
+          <t>Chế Tạo Thuốc</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Công thức</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Kỷ lục đã được cập nhật</t>
+          <t>Bản ghi đã được cập nhật</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Làm mới sau 1 phút</t>
+          <t>Làm mới sau 1 phút nữa</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Reported</t>
+          <t>Đã báo cáo</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Đã nhận toàn bộ phần thưởng Influence</t>
+          <t>Đã nhận toàn bộ phần thưởng Ảnh Hưởng</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Re-simulate</t>
+          <t>Tái mô phỏng</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ.</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Syntonized</t>
+          <t>Đã điều tần</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Vật phẩm đang trong Cooldown</t>
+          <t>Vật phẩm đang hồi chiêu</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>NOVICE</t>
+          <t>NGƯỜI MỚI</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Cấp độ Echo</t>
+          <t>Cấp Độ Echo</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>INTERMEDIATE</t>
+          <t>TRUNG CẤP</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>ADVANCED</t>
+          <t>NÂNG CAO</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>AVERAGE</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Cấp độ nhân vật</t>
+          <t>Cấp độ Nhân vật</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Cấp độ vũ khí</t>
+          <t>Cấp Độ Vũ Khí</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>%s giai đoạn</t>
+          <t>%s sân khấu</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Ascend</t>
+          <t>Thăng hoa</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Shell Credit Owned</t>
+          <t>Shell Credit Đang Sở Hữu</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Attributes</t>
+          <t>Thuộc tính</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Upgraded</t>
+          <t>Đã nâng cấp</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Lên Cấp</t>
+          <t>Nâng cấp Nhiệm vụ</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Chưa Nhận Được</t>
+          <t>Chưa nhận được</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Đạt cấp tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>New Effect</t>
+          <t>Hiệu Ứng Mới</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ.</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Insufficient Shell Credit</t>
+          <t>Tín dụng Vỏ sò không đủ</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Không thể xem chi tiết Echo của nhân vật thử nghiệm</t>
+          <t>Không thể xem chi tiết Echo của Nhân Vật Thử Nghiệm</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Đã đạt giá trị tối đa</t>
+          <t>Đạt giá trị tối đa</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Cấp Độ Tiếp Theo</t>
+          <t>Cấp độ tiếp theo</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Sort By Date Acquired</t>
+          <t>Sắp xếp theo Ngày Nhận</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Sắp xếp theo Cấp độ</t>
+          <t>Sắp xếp theo Cấp Độ</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Sort By Rarity</t>
+          <t>Sắp xếp theo Độ Hiếm</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>(Đang chờ kích hoạt)</t>
+          <t>Đang chờ kích hoạt</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Nhân Vật</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
